--- a/ARM Functions/Item Edits/Squirtilium Z.xlsx
+++ b/ARM Functions/Item Edits/Squirtilium Z.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\Modded ROM\USUM ARM research\Item Edits\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Item Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3877320C-8634-4F80-8325-5E03A8EA50C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203F7BDF-6FCE-4AC2-A51D-B0659380E286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Edited main" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Address</t>
   </si>
@@ -86,12 +86,6 @@
     <t>00000000</t>
   </si>
   <si>
-    <t>mov r1, 0x2</t>
-  </si>
-  <si>
-    <t>0210A0E3</t>
-  </si>
-  <si>
     <t>mov r0, r1</t>
   </si>
   <si>
@@ -101,98 +95,113 @@
     <t>bl 0x00092298</t>
   </si>
   <si>
-    <t>push {r2, lr}</t>
-  </si>
-  <si>
     <t>ldrh r1, [r0, 0xC]</t>
   </si>
   <si>
-    <t>cmp r0, 0x7</t>
-  </si>
-  <si>
     <t>cmp r9, 0x43</t>
   </si>
   <si>
     <t>beq 0x000FDA28</t>
   </si>
   <si>
-    <t>b 0x000FD568</t>
-  </si>
-  <si>
-    <t>0x43/0x41 call respective Loaded Dice function if Apex Squirtle</t>
-  </si>
-  <si>
     <t>000DB17C</t>
   </si>
   <si>
-    <t>000FFF3C</t>
-  </si>
-  <si>
-    <t>04402DE9</t>
-  </si>
-  <si>
     <t>0100A0E1</t>
   </si>
   <si>
     <t>0210A0E1</t>
   </si>
   <si>
-    <t>D248FEEB</t>
-  </si>
-  <si>
     <t>BC10D0E1</t>
   </si>
   <si>
-    <t>070050E3</t>
-  </si>
-  <si>
-    <t>0440BDE8</t>
-  </si>
-  <si>
     <t>430059E3</t>
   </si>
   <si>
-    <t>0480BDE8</t>
-  </si>
-  <si>
     <t>Get Pointer</t>
   </si>
   <si>
     <t>Check species for Squirtle</t>
   </si>
   <si>
-    <t>ldr r1, [r0, 0x239]</t>
-  </si>
-  <si>
-    <t>cmp r1, 0x0</t>
-  </si>
-  <si>
     <t>Don't run if not Apex</t>
   </si>
   <si>
-    <t>0600001A</t>
-  </si>
-  <si>
-    <t>391290E5</t>
-  </si>
-  <si>
-    <t>000051E3</t>
-  </si>
-  <si>
-    <t>0300000A</t>
-  </si>
-  <si>
-    <t>ADF6FF0A</t>
-  </si>
-  <si>
-    <t>7CF5FFEA</t>
+    <t>push {r0, r1, r2, r3, lr}</t>
+  </si>
+  <si>
+    <t>0F402DE9</t>
+  </si>
+  <si>
+    <t>0F40BDE8</t>
+  </si>
+  <si>
+    <t>0F80BDE8</t>
+  </si>
+  <si>
+    <t>ldrbeq r1, [r0, 0x239]</t>
+  </si>
+  <si>
+    <t>cmp r1, 0x1</t>
+  </si>
+  <si>
+    <t>cmpne r1, 0x2</t>
+  </si>
+  <si>
+    <t>blo 0x000FD568</t>
+  </si>
+  <si>
+    <t>bhi 0x000FFC34</t>
+  </si>
+  <si>
+    <t>0310A0E3</t>
+  </si>
+  <si>
+    <t>mov r1, 0x3</t>
+  </si>
+  <si>
+    <t>cmp r1, 0x7</t>
+  </si>
+  <si>
+    <t>Squirtilium Z Loaded Dice + Apex Transform 0x41/0x43/0x9E</t>
+  </si>
+  <si>
+    <t>000BBA10</t>
+  </si>
+  <si>
+    <t>1D5AFFEB</t>
+  </si>
+  <si>
+    <t>070051E3</t>
+  </si>
+  <si>
+    <t>3912D005</t>
+  </si>
+  <si>
+    <t>010051E3</t>
+  </si>
+  <si>
+    <t>02005113</t>
+  </si>
+  <si>
+    <t>0400001A</t>
+  </si>
+  <si>
+    <t>F807010A</t>
+  </si>
+  <si>
+    <t>C706013A</t>
+  </si>
+  <si>
+    <t>7910018A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,15 +213,19 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <color theme="1"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="5">
@@ -253,19 +266,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -600,366 +614,332 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD17F403-0334-4F0F-BD62-1976F89E9C58}">
-  <dimension ref="A1:K44"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
-    <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="9.35546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.0703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.92578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="str">
+    <row r="3" spans="1:11">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="2" t="str">
         <f>DEC2HEX(HEX2DEC(A3)+4,8)</f>
         <v>000DB180</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="str">
+    <row r="5" spans="1:11">
+      <c r="A5" s="2" t="str">
         <f t="shared" ref="A5:A7" si="0">DEC2HEX(HEX2DEC(A4)+4,8)</f>
         <v>000DB184</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="str">
+    <row r="6" spans="1:11">
+      <c r="A6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000DB188</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="str">
+    <row r="7" spans="1:11">
+      <c r="A7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000DB18C</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4" t="str">
+        <f>DEC2HEX(HEX2DEC(A10)+4,8)</f>
+        <v>000BBA14</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="4" t="str">
+        <f t="shared" ref="A12:A25" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
+        <v>000BBA18</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA1C</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA20</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA24</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA28</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA2C</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA30</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA34</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="9" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$25)</f>
+        <v>bne 0x000BBA4C</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA38</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="2" t="str">
+        <f>SUBSTITUTE(C10,"push","pop")</f>
+        <v>pop {r0, r1, r2, r3, lr}</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA3C</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA40</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" s="5" t="str">
-        <f>DEC2HEX(HEX2DEC(A10)+4,8)</f>
-        <v>000FFF40</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" s="5" t="str">
-        <f t="shared" ref="A12:A24" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
-        <v>000FFF44</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF48</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA44</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="12"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA48</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>000BBA4C</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A14" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF4C</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A15" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF50</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A16" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF54</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="6" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$24)</f>
-        <v>bne 0x000FFF74</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF58</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF5C</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF60</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="9" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A$24)</f>
-        <v>beq 0x000FFF74</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF64</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="str">
-        <f>SUBSTITUTE(C10,"push","pop")</f>
-        <v>pop {r2, lr}</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A21" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF68</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A22" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF6C</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF70</v>
-      </c>
-      <c r="B23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" t="str">
-        <f t="shared" si="1"/>
-        <v>000FFF74</v>
-      </c>
-      <c r="B24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="2" t="str">
+      <c r="C25" s="8" t="str">
         <f>SUBSTITUTE(C20,"lr","pc")</f>
-        <v>pop {r2, pc}</v>
-      </c>
-      <c r="E24" t="str">
-        <f>REPT("cc",COUNTA(A10:A24)*4)</f>
-        <v>cccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccccc</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B30" s="1"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B31" s="1"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B32" s="1"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B34" s="1"/>
-      <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="K35" s="3"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B39" s="2"/>
-      <c r="D39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B40" s="2"/>
-      <c r="D40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B41" s="2"/>
-      <c r="D41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B42" s="2"/>
-      <c r="D42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B43" s="2"/>
-      <c r="D43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A44" s="4"/>
+        <v>pop {r0, r1, r2, r3, pc}</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
